--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
+++ b/ValueSet-ukhd-an-behandlungsstatus-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
